--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N78_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.27635439253599</v>
+        <v>6.382407588787099</v>
       </c>
       <c r="D2" t="n">
-        <v>38.82514780692573</v>
+        <v>6.309086518625432</v>
       </c>
       <c r="E2" t="n">
-        <v>10.64671943723436</v>
+        <v>1.730091908550583</v>
       </c>
       <c r="F2" t="n">
-        <v>12.99631702789948</v>
+        <v>2.111901517033665</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.54926766658093</v>
+        <v>5.289255995819402</v>
       </c>
       <c r="D3" t="n">
-        <v>32.29894589762366</v>
+        <v>5.248578708363845</v>
       </c>
       <c r="E3" t="n">
-        <v>10.64671943723436</v>
+        <v>1.730091908550583</v>
       </c>
       <c r="F3" t="n">
-        <v>12.99631702789948</v>
+        <v>2.111901517033665</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.36045556672211</v>
+        <v>4.121074029592343</v>
       </c>
       <c r="D4" t="n">
-        <v>24.92554335565713</v>
+        <v>4.050400795294284</v>
       </c>
       <c r="E4" t="n">
-        <v>10.64671943723436</v>
+        <v>1.730091908550583</v>
       </c>
       <c r="F4" t="n">
-        <v>12.99631702789948</v>
+        <v>2.111901517033665</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.80758221065778</v>
+        <v>5.981232109231889</v>
       </c>
       <c r="D5" t="n">
-        <v>36.74328578440547</v>
+        <v>5.970783939965888</v>
       </c>
       <c r="E5" t="n">
-        <v>10.64671943723436</v>
+        <v>1.730091908550583</v>
       </c>
       <c r="F5" t="n">
-        <v>12.99631702789948</v>
+        <v>2.111901517033665</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.85811195529209</v>
+        <v>2.739443192734965</v>
       </c>
       <c r="D6" t="n">
-        <v>16.42294736285506</v>
+        <v>2.668728946463948</v>
       </c>
       <c r="E6" t="n">
-        <v>10.64671943723436</v>
+        <v>1.730091908550583</v>
       </c>
       <c r="F6" t="n">
-        <v>12.99631702789948</v>
+        <v>2.111901517033665</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.47451222527948</v>
+        <v>5.277108236607915</v>
       </c>
       <c r="D7" t="n">
-        <v>23.18368692613566</v>
+        <v>3.767349125497045</v>
       </c>
       <c r="E7" t="n">
-        <v>10.64671943723436</v>
+        <v>1.730091908550583</v>
       </c>
       <c r="F7" t="n">
-        <v>12.99631702789948</v>
+        <v>2.111901517033665</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.38978466615652</v>
+        <v>6.563340008250435</v>
       </c>
       <c r="D8" t="n">
-        <v>13.12497308326543</v>
+        <v>2.132808126030632</v>
       </c>
       <c r="E8" t="n">
-        <v>10.64671943723436</v>
+        <v>1.730091908550583</v>
       </c>
       <c r="F8" t="n">
-        <v>12.99631702789948</v>
+        <v>2.111901517033665</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.12451428427411</v>
+        <v>2.132733571194543</v>
       </c>
       <c r="D9" t="n">
-        <v>12.96578416724109</v>
+        <v>2.106939927176677</v>
       </c>
       <c r="E9" t="n">
-        <v>10.64671943723436</v>
+        <v>1.730091908550583</v>
       </c>
       <c r="F9" t="n">
-        <v>12.99631702789948</v>
+        <v>2.111901517033665</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.01493714381291</v>
+        <v>6.177427285869598</v>
       </c>
       <c r="D10" t="n">
-        <v>14.7323011973257</v>
+        <v>2.393998944565427</v>
       </c>
       <c r="E10" t="n">
-        <v>10.64671943723436</v>
+        <v>1.730091908550583</v>
       </c>
       <c r="F10" t="n">
-        <v>12.99631702789948</v>
+        <v>2.111901517033665</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.53618830438601</v>
+        <v>6.912130599462727</v>
       </c>
       <c r="D11" t="n">
-        <v>42.85803648548816</v>
+        <v>6.964430928891826</v>
       </c>
       <c r="E11" t="n">
-        <v>10.64671943723436</v>
+        <v>1.730091908550583</v>
       </c>
       <c r="F11" t="n">
-        <v>12.99631702789948</v>
+        <v>2.111901517033665</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>49.02742179632399</v>
+        <v>7.966956041902649</v>
       </c>
       <c r="D12" t="n">
-        <v>49.46863175892766</v>
+        <v>8.038652660825745</v>
       </c>
       <c r="E12" t="n">
-        <v>10.64671943723436</v>
+        <v>1.730091908550583</v>
       </c>
       <c r="F12" t="n">
-        <v>12.99631702789948</v>
+        <v>2.111901517033665</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>46.74312536802432</v>
+        <v>7.595757872303952</v>
       </c>
       <c r="D13" t="n">
-        <v>47.13848101970456</v>
+        <v>7.66000316570199</v>
       </c>
       <c r="E13" t="n">
-        <v>10.64671943723436</v>
+        <v>1.730091908550583</v>
       </c>
       <c r="F13" t="n">
-        <v>12.99631702789948</v>
+        <v>2.111901517033665</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
